--- a/artfynd/A 14245-2025 artfynd.xlsx
+++ b/artfynd/A 14245-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109672394</v>
+        <v>109672391</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407928.917497518</v>
+        <v>407439</v>
       </c>
       <c r="R2" t="n">
-        <v>7014334.335588082</v>
+        <v>7014589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,14 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>109672392</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407663.9694178636</v>
+        <v>407664</v>
       </c>
       <c r="R3" t="n">
-        <v>7014508.711146449</v>
+        <v>7014509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109672391</v>
+        <v>109672393</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407439.228131063</v>
+        <v>407883</v>
       </c>
       <c r="R4" t="n">
-        <v>7014589.088308994</v>
+        <v>7014323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +959,9 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109672393</v>
+        <v>109672394</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407882.9882897477</v>
+        <v>407929</v>
       </c>
       <c r="R5" t="n">
-        <v>7014322.575465055</v>
+        <v>7014335</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,24 +1065,14 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14245-2025 artfynd.xlsx
+++ b/artfynd/A 14245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109672391</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109672392</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109672393</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109672394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>